--- a/data/trans_orig/P6906-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6906-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21575</t>
+          <t>21779</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>10242</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11097</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28011</t>
+          <t>27458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89711</t>
+          <t>89507</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104045</t>
+          <t>103528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27290</t>
+          <t>27326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35635</t>
+          <t>35600</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120843</t>
+          <t>121396</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137757</t>
+          <t>137536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>54744</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84574</t>
+          <t>85190</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38586</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80022</t>
+          <t>78439</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116171</t>
+          <t>115444</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202371</t>
+          <t>201755</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>234225</t>
+          <t>232201</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79985</t>
+          <t>80575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>98361</t>
+          <t>98683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>289344</t>
+          <t>290071</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>325493</t>
+          <t>327076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34242</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21261</t>
+          <t>21468</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29432</t>
+          <t>29566</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51275</t>
+          <t>50861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39833</t>
+          <t>39874</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55859</t>
+          <t>56928</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42722</t>
+          <t>42515</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55423</t>
+          <t>55264</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86783</t>
+          <t>87197</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>108626</t>
+          <t>108492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88075</t>
+          <t>89686</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126925</t>
+          <t>126337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>36169</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60513</t>
+          <t>62153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133854</t>
+          <t>132408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177728</t>
+          <t>178065</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345380</t>
+          <t>345968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>384230</t>
+          <t>382619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>159608</t>
+          <t>157968</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183422</t>
+          <t>183952</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>514699</t>
+          <t>514362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>558573</t>
+          <t>560019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20426</t>
+          <t>20881</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>14289</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14064</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>29785</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37278</t>
+          <t>36823</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50285</t>
+          <t>49531</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24551</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34093</t>
+          <t>34191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65191</t>
+          <t>65853</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81574</t>
+          <t>81771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44200</t>
+          <t>42864</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71816</t>
+          <t>69223</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29748</t>
+          <t>31070</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52424</t>
+          <t>53685</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78850</t>
+          <t>80148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113159</t>
+          <t>113974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>149657</t>
+          <t>152250</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>177273</t>
+          <t>178609</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78155</t>
+          <t>76894</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100831</t>
+          <t>99509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>238894</t>
+          <t>238079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>273203</t>
+          <t>271905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22331</t>
+          <t>22942</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21724</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20485</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39597</t>
+          <t>39849</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,12%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36766</t>
+          <t>36530</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24597</t>
+          <t>24255</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37786</t>
+          <t>37301</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52813</t>
+          <t>52561</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71925</t>
+          <t>71341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69303</t>
+          <t>69536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101467</t>
+          <t>101114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50884</t>
+          <t>50686</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77900</t>
+          <t>78378</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127674</t>
+          <t>128721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170148</t>
+          <t>171769</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>223799</t>
+          <t>224152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>255963</t>
+          <t>255730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136935</t>
+          <t>136457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163951</t>
+          <t>164149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>369953</t>
+          <t>368332</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412427</t>
+          <t>411380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,17%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24951</t>
+          <t>25485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36055</t>
+          <t>35814</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48930</t>
+          <t>50169</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16076</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48654</t>
+          <t>48120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63228</t>
+          <t>63826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32590</t>
+          <t>32668</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57215</t>
+          <t>56396</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29785</t>
+          <t>30781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50045</t>
+          <t>50809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68658</t>
+          <t>66470</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101817</t>
+          <t>99133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172167</t>
+          <t>172986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>196792</t>
+          <t>196714</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74520</t>
+          <t>73756</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94780</t>
+          <t>93784</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>252130</t>
+          <t>254814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>285289</t>
+          <t>287477</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>81,22%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18980</t>
+          <t>18832</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35749</t>
+          <t>35978</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17109</t>
+          <t>17113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35287</t>
+          <t>34208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40852</t>
+          <t>41862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65874</t>
+          <t>65136</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,46%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27779</t>
+          <t>27550</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44548</t>
+          <t>44696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38421</t>
+          <t>39500</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56599</t>
+          <t>56595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>72100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>96384</t>
+          <t>95374</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66128</t>
+          <t>66294</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100606</t>
+          <t>102263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57639</t>
+          <t>55820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85697</t>
+          <t>83491</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133355</t>
+          <t>133561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177427</t>
+          <t>177388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>247885</t>
+          <t>246228</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>282363</t>
+          <t>282197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130601</t>
+          <t>132807</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>158659</t>
+          <t>160478</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>387361</t>
+          <t>387400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431433</t>
+          <t>431227</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,35%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene problemas de sueño en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>21297</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>28187</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16514</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23493</t>
+          <t>23246</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41288</t>
+          <t>41301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50231</t>
+          <t>50101</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29599</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54198</t>
+          <t>56140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31938</t>
+          <t>33255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66967</t>
+          <t>68688</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73644</t>
+          <t>73032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113692</t>
+          <t>114294</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185382</t>
+          <t>183440</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209981</t>
+          <t>209585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>171401</t>
+          <t>169680</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>206430</t>
+          <t>205113</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>364256</t>
+          <t>363654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404304</t>
+          <t>404916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>11873</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28688</t>
+          <t>30051</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23821</t>
+          <t>24697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39938</t>
+          <t>41758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39718</t>
+          <t>40449</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64309</t>
+          <t>65236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40838</t>
+          <t>39475</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58333</t>
+          <t>57653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50757</t>
+          <t>48937</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66874</t>
+          <t>65998</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95912</t>
+          <t>94985</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120503</t>
+          <t>119772</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,75%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50361</t>
+          <t>48058</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83856</t>
+          <t>81401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62869</t>
+          <t>65386</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106274</t>
+          <t>105993</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125181</t>
+          <t>128663</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176510</t>
+          <t>179161</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>254464</t>
+          <t>256919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>287959</t>
+          <t>290262</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>247775</t>
+          <t>248056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>291180</t>
+          <t>288663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>515859</t>
+          <t>513208</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>567188</t>
+          <t>563706</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
